--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Composition.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -511,6 +511,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Composition.meta.tag</t>
   </si>
   <si>
@@ -639,9 +646,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Erweiterungen für die Composition, die durch url unterschieden werden sollen</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -658,10 +662,6 @@
     <t>Die ID des Begünstigten des E-Rezept-Belegs (z. B. TelematikID der Apotheke)</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Composition.modifierExtension</t>
   </si>
   <si>
@@ -894,6 +894,9 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -1001,6 +1004,10 @@
     <t>Essential metadata for searching for the composition. Identifies who and/or what the composition/document is about.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
   </si>
   <si>
@@ -1026,6 +1033,9 @@
     <t>Describes the clinical encounter or type of care this documentation is associated with.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Provides context for the composition and supports searching.</t>
   </si>
   <si>
@@ -1447,6 +1457,14 @@
   </si>
   <si>
     <t>The period of time covered by the documentation. There is no assertion that the documentation is a complete representation for this period, only that it documents events during this time.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>DocumentReference.event.period</t>
@@ -1605,8 +1623,8 @@
     <t>The root of the sections that make up the composition.</t>
   </si>
   <si>
-    <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
-cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}</t>
   </si>
   <si>
     <t>./outboundRelationship[typeCode="COMP" and isNormalActRelationship()]/target[moodCode="EVN" and classCode="DOCSECT" and isNormalAct]</t>
@@ -1690,6 +1708,9 @@
     <t>Typically, sections in a doument are about the subject of the document, whether that is a  patient, or group of patients, location, or device, or whatever. For some kind of documents, some sections actually contain data about related entities. Typical examples are  a section in a newborn discharge summary concerning the mother, or family history documents, with a section about each family member, though there are many other examples.</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>.subject? (CDA did not differentiate between subject and focus)</t>
   </si>
   <si>
@@ -1703,119 +1724,123 @@
   </si>
   <si>
     <t>Document profiles may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>ele-1
+cmp-1</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>Composition.section.mode</t>
+  </si>
+  <si>
+    <t>working | snapshot | changes</t>
+  </si>
+  <si>
+    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
+  </si>
+  <si>
+    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
+  </si>
+  <si>
+    <t>The processing mode that applies to this section.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
+  </si>
+  <si>
+    <t>Composition.section.orderedBy</t>
+  </si>
+  <si>
+    <t>Order of section entries</t>
+  </si>
+  <si>
+    <t>Specifies the order applied to the items in the section entries.</t>
+  </si>
+  <si>
+    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
+  </si>
+  <si>
+    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
+  </si>
+  <si>
+    <t>What order applies to the items in the entry.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
+  </si>
+  <si>
+    <t>Composition.section.entry</t>
+  </si>
+  <si>
+    <t>A reference to data that supports this section</t>
+  </si>
+  <si>
+    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
+  </si>
+  <si>
+    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
+  </si>
+  <si>
+    <t>ele-1
+cmp-2</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>.entry</t>
+  </si>
+  <si>
+    <t>Composition.section.emptyReason</t>
+  </si>
+  <si>
+    <t>Why the section is empty</t>
+  </si>
+  <si>
+    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
+  </si>
+  <si>
+    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
+  </si>
+  <si>
+    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
+  </si>
+  <si>
+    <t>If a section is empty, why it is empty.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
+  </si>
+  <si>
+    <t>Composition.section.section</t>
+  </si>
+  <si>
+    <t>Nested Section</t>
+  </si>
+  <si>
+    <t>A nested sub-section within this section.</t>
+  </si>
+  <si>
+    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t xml:space="preserve">cmp-1
 </t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>Composition.section.mode</t>
-  </si>
-  <si>
-    <t>working | snapshot | changes</t>
-  </si>
-  <si>
-    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
-  </si>
-  <si>
-    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
-  </si>
-  <si>
-    <t>The processing mode that applies to this section.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
-  </si>
-  <si>
-    <t>Composition.section.orderedBy</t>
-  </si>
-  <si>
-    <t>Order of section entries</t>
-  </si>
-  <si>
-    <t>Specifies the order applied to the items in the section entries.</t>
-  </si>
-  <si>
-    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
-  </si>
-  <si>
-    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
-  </si>
-  <si>
-    <t>What order applies to the items in the entry.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
-  </si>
-  <si>
-    <t>Composition.section.entry</t>
-  </si>
-  <si>
-    <t>A reference to data that supports this section</t>
-  </si>
-  <si>
-    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
-  </si>
-  <si>
-    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cmp-2
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>.entry</t>
-  </si>
-  <si>
-    <t>Composition.section.emptyReason</t>
-  </si>
-  <si>
-    <t>Why the section is empty</t>
-  </si>
-  <si>
-    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
-  </si>
-  <si>
-    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
-  </si>
-  <si>
-    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
-  </si>
-  <si>
-    <t>If a section is empty, why it is empty.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
-  </si>
-  <si>
-    <t>Composition.section.section</t>
-  </si>
-  <si>
-    <t>Nested Section</t>
-  </si>
-  <si>
-    <t>A nested sub-section within this section.</t>
-  </si>
-  <si>
-    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t>.component.section</t>
@@ -2166,7 +2191,7 @@
     <col min="26" max="26" width="63.30859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="62.5390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3569,7 +3594,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>103</v>
@@ -3578,7 +3603,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -3592,10 +3617,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3621,13 +3646,13 @@
         <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3653,13 +3678,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3677,7 +3702,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3686,7 +3711,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
@@ -3695,7 +3720,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3709,10 +3734,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3738,13 +3763,13 @@
         <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3794,7 +3819,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3826,10 +3851,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3852,16 +3877,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3887,13 +3912,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3911,7 +3936,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3943,14 +3968,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3969,16 +3994,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4028,7 +4053,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4046,7 +4071,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -4060,14 +4085,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4086,16 +4111,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4145,7 +4170,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4163,7 +4188,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -4177,10 +4202,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4206,10 +4231,10 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4251,7 +4276,7 @@
         <v>116</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
@@ -4260,7 +4285,7 @@
         <v>145</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4292,13 +4317,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4320,13 +4345,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4377,7 +4402,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4386,7 +4411,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>120</v>
@@ -4484,16 +4509,16 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>211</v>
@@ -4514,7 +4539,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4622,7 +4647,7 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
@@ -4671,7 +4696,7 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>223</v>
@@ -4827,7 +4852,7 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y23" t="s" s="2">
         <v>241</v>
@@ -4860,7 +4885,7 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
@@ -5209,7 +5234,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -5726,7 +5751,7 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>275</v>
@@ -5851,16 +5876,18 @@
       <c r="M32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -5902,7 +5929,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5920,7 +5947,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5934,10 +5961,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5960,19 +5987,19 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6021,7 +6048,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6039,7 +6066,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6053,10 +6080,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6082,16 +6109,16 @@
         <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6140,7 +6167,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6158,7 +6185,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6172,10 +6199,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6201,16 +6228,16 @@
         <v>236</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6235,13 +6262,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6259,7 +6286,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6268,22 +6295,22 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>247</v>
@@ -6291,10 +6318,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6317,19 +6344,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6378,7 +6405,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6387,33 +6414,33 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6436,17 +6463,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6495,7 +6524,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6504,33 +6533,33 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6553,19 +6582,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6614,7 +6643,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6629,27 +6658,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6672,17 +6701,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6731,7 +6762,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6740,33 +6771,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6792,13 +6823,13 @@
         <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6806,7 +6837,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>78</v>
@@ -6848,7 +6879,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6866,13 +6897,13 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -6880,10 +6911,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6906,16 +6937,16 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6944,10 +6975,10 @@
         <v>228</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6965,7 +6996,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6983,13 +7014,13 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -6997,10 +7028,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7023,19 +7054,19 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7084,7 +7115,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7093,7 +7124,7 @@
         <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -7102,13 +7133,13 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7116,10 +7147,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7231,10 +7262,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7304,16 +7335,16 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>119</v>
@@ -7348,14 +7379,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7377,10 +7408,10 @@
         <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>115</v>
@@ -7435,7 +7466,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7453,7 +7484,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7467,10 +7498,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7493,17 +7524,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7531,10 +7562,10 @@
         <v>228</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7552,7 +7583,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7570,10 +7601,10 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7584,10 +7615,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7610,17 +7641,17 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7669,7 +7700,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7687,10 +7718,10 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7701,10 +7732,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7727,17 +7758,19 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7786,7 +7819,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7795,33 +7828,33 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7844,19 +7877,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7905,7 +7938,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7914,22 +7947,22 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7937,10 +7970,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7963,16 +7996,16 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8022,7 +8055,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8031,7 +8064,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -8040,13 +8073,13 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8054,10 +8087,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8169,10 +8202,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8242,16 +8275,16 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>119</v>
@@ -8286,14 +8319,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8315,10 +8348,10 @@
         <v>112</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>115</v>
@@ -8373,7 +8406,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8391,7 +8424,7 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8405,10 +8438,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8431,16 +8464,16 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8469,10 +8502,10 @@
         <v>228</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8490,7 +8523,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>91</v>
@@ -8508,13 +8541,13 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8522,10 +8555,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8548,13 +8581,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8605,7 +8638,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8614,7 +8647,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -8623,13 +8656,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8637,10 +8670,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8663,19 +8696,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8724,7 +8757,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8733,7 +8766,7 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>103</v>
@@ -8742,13 +8775,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8756,10 +8789,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8871,10 +8904,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8944,16 +8977,16 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>119</v>
@@ -8988,14 +9021,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9017,10 +9050,10 @@
         <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>115</v>
@@ -9075,7 +9108,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9093,7 +9126,7 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9107,10 +9140,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9136,13 +9169,13 @@
         <v>236</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9168,13 +9201,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9192,7 +9225,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9201,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9216,7 +9249,7 @@
         <v>245</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9224,10 +9257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9250,15 +9283,17 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9307,7 +9342,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9316,22 +9351,22 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>468</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9339,10 +9374,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9454,10 +9489,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9571,10 +9606,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9597,16 +9632,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9656,7 +9691,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9665,7 +9700,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9674,7 +9709,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9688,10 +9723,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9714,23 +9749,23 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>78</v>
@@ -9775,7 +9810,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9784,7 +9819,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -9793,7 +9828,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9807,10 +9842,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9833,15 +9868,17 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9890,7 +9927,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9899,16 +9936,16 @@
         <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>109</v>
@@ -9922,10 +9959,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10037,10 +10074,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10154,10 +10191,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10183,13 +10220,13 @@
         <v>105</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10239,7 +10276,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10248,7 +10285,7 @@
         <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>103</v>
@@ -10257,7 +10294,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10271,10 +10308,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10300,13 +10337,13 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10335,10 +10372,10 @@
         <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10356,7 +10393,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10374,7 +10411,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10388,10 +10425,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10417,13 +10454,13 @@
         <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10473,7 +10510,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10482,7 +10519,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -10491,7 +10528,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10505,10 +10542,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10534,13 +10571,13 @@
         <v>105</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10590,7 +10627,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10608,7 +10645,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10622,10 +10659,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10648,13 +10685,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10705,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10714,19 +10751,19 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10737,10 +10774,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10852,10 +10889,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10925,16 +10962,16 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>119</v>
@@ -10969,14 +11006,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10998,10 +11035,10 @@
         <v>112</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>115</v>
@@ -11056,7 +11093,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11074,7 +11111,7 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -11088,14 +11125,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11117,16 +11154,16 @@
         <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11175,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11193,10 +11230,10 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11207,10 +11244,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11236,16 +11273,16 @@
         <v>236</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11270,32 +11307,32 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
@@ -11303,7 +11340,7 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
@@ -11326,10 +11363,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11352,17 +11389,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11411,7 +11450,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11420,33 +11459,33 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11469,16 +11508,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11528,7 +11567,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11537,19 +11576,19 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11560,10 +11599,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11586,16 +11625,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11645,7 +11684,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11654,7 +11693,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11663,10 +11702,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11677,10 +11716,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11703,19 +11742,19 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11743,28 +11782,28 @@
         <v>228</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="Z82" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11782,7 +11821,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>109</v>
@@ -11796,10 +11835,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11825,16 +11864,16 @@
         <v>236</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11859,32 +11898,32 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="Z83" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AA83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
@@ -11892,7 +11931,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -11901,7 +11940,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>109</v>
@@ -11915,10 +11954,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11941,16 +11980,16 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12000,7 +12039,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12009,19 +12048,19 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12032,10 +12071,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12061,16 +12100,16 @@
         <v>236</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -12095,32 +12134,32 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="Z85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
@@ -12128,7 +12167,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12137,7 +12176,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>109</v>
@@ -12151,10 +12190,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12180,13 +12219,13 @@
         <v>81</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12236,7 +12275,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12245,19 +12284,19 @@
         <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>546</v>
+        <v>589</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Composition.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="584">
   <si>
     <t>Property</t>
   </si>
@@ -511,157 +511,157 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>Composition.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Composition.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Composition.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Composition.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Composition.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Composition.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Erweiterungen für die Composition, die durch url unterschieden werden sollen</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Composition.extension:Beneficiary</t>
+  </si>
+  <si>
+    <t>Beneficiary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_Beneficiary}
+</t>
+  </si>
+  <si>
+    <t>Die ID des Begünstigten des E-Rezept-Belegs (z. B. TelematikID der Apotheke)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Composition.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Composition.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Composition.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Composition.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Composition.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Composition.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Composition.extension:Beneficiary</t>
-  </si>
-  <si>
-    <t>Beneficiary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_Beneficiary}
-</t>
-  </si>
-  <si>
-    <t>Die ID des Begünstigten des E-Rezept-Belegs (z. B. TelematikID der Apotheke)</t>
-  </si>
-  <si>
     <t>Composition.modifierExtension</t>
   </si>
   <si>
@@ -894,9 +894,6 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -1004,10 +1001,6 @@
     <t>Essential metadata for searching for the composition. Identifies who and/or what the composition/document is about.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
   </si>
   <si>
@@ -1033,9 +1026,6 @@
     <t>Describes the clinical encounter or type of care this documentation is associated with.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Provides context for the composition and supports searching.</t>
   </si>
   <si>
@@ -1457,14 +1447,6 @@
   </si>
   <si>
     <t>The period of time covered by the documentation. There is no assertion that the documentation is a complete representation for this period, only that it documents events during this time.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>DocumentReference.event.period</t>
@@ -1623,8 +1605,8 @@
     <t>The root of the sections that make up the composition.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}</t>
+    <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
+cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>./outboundRelationship[typeCode="COMP" and isNormalActRelationship()]/target[moodCode="EVN" and classCode="DOCSECT" and isNormalAct]</t>
@@ -1708,9 +1690,6 @@
     <t>Typically, sections in a doument are about the subject of the document, whether that is a  patient, or group of patients, location, or device, or whatever. For some kind of documents, some sections actually contain data about related entities. Typical examples are  a section in a newborn discharge summary concerning the mother, or family history documents, with a section about each family member, though there are many other examples.</t>
   </si>
   <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>.subject? (CDA did not differentiate between subject and focus)</t>
   </si>
   <si>
@@ -1724,123 +1703,119 @@
   </si>
   <si>
     <t>Document profiles may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>ele-1
-cmp-1</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>Composition.section.mode</t>
-  </si>
-  <si>
-    <t>working | snapshot | changes</t>
-  </si>
-  <si>
-    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
-  </si>
-  <si>
-    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
-  </si>
-  <si>
-    <t>The processing mode that applies to this section.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
-  </si>
-  <si>
-    <t>Composition.section.orderedBy</t>
-  </si>
-  <si>
-    <t>Order of section entries</t>
-  </si>
-  <si>
-    <t>Specifies the order applied to the items in the section entries.</t>
-  </si>
-  <si>
-    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
-  </si>
-  <si>
-    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
-  </si>
-  <si>
-    <t>What order applies to the items in the entry.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
-  </si>
-  <si>
-    <t>Composition.section.entry</t>
-  </si>
-  <si>
-    <t>A reference to data that supports this section</t>
-  </si>
-  <si>
-    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
-  </si>
-  <si>
-    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
-  </si>
-  <si>
-    <t>ele-1
-cmp-2</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>.entry</t>
-  </si>
-  <si>
-    <t>Composition.section.emptyReason</t>
-  </si>
-  <si>
-    <t>Why the section is empty</t>
-  </si>
-  <si>
-    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
-  </si>
-  <si>
-    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
-  </si>
-  <si>
-    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
-  </si>
-  <si>
-    <t>If a section is empty, why it is empty.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
-  </si>
-  <si>
-    <t>Composition.section.section</t>
-  </si>
-  <si>
-    <t>Nested Section</t>
-  </si>
-  <si>
-    <t>A nested sub-section within this section.</t>
-  </si>
-  <si>
-    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t xml:space="preserve">cmp-1
 </t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>Composition.section.mode</t>
+  </si>
+  <si>
+    <t>working | snapshot | changes</t>
+  </si>
+  <si>
+    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
+  </si>
+  <si>
+    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
+  </si>
+  <si>
+    <t>The processing mode that applies to this section.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
+  </si>
+  <si>
+    <t>Composition.section.orderedBy</t>
+  </si>
+  <si>
+    <t>Order of section entries</t>
+  </si>
+  <si>
+    <t>Specifies the order applied to the items in the section entries.</t>
+  </si>
+  <si>
+    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
+  </si>
+  <si>
+    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
+  </si>
+  <si>
+    <t>What order applies to the items in the entry.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
+  </si>
+  <si>
+    <t>Composition.section.entry</t>
+  </si>
+  <si>
+    <t>A reference to data that supports this section</t>
+  </si>
+  <si>
+    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
+  </si>
+  <si>
+    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cmp-2
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>.entry</t>
+  </si>
+  <si>
+    <t>Composition.section.emptyReason</t>
+  </si>
+  <si>
+    <t>Why the section is empty</t>
+  </si>
+  <si>
+    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
+  </si>
+  <si>
+    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
+  </si>
+  <si>
+    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
+  </si>
+  <si>
+    <t>If a section is empty, why it is empty.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
+  </si>
+  <si>
+    <t>Composition.section.section</t>
+  </si>
+  <si>
+    <t>Nested Section</t>
+  </si>
+  <si>
+    <t>A nested sub-section within this section.</t>
+  </si>
+  <si>
+    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t>.component.section</t>
@@ -2191,7 +2166,7 @@
     <col min="26" max="26" width="63.30859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="62.5390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3594,7 +3569,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>103</v>
@@ -3603,7 +3578,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -3617,10 +3592,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3646,13 +3621,13 @@
         <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3678,31 +3653,31 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3711,7 +3686,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
@@ -3720,7 +3695,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3734,10 +3709,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3763,13 +3738,13 @@
         <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3819,7 +3794,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3851,10 +3826,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3877,16 +3852,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3912,31 +3887,31 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3968,14 +3943,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3994,16 +3969,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4053,7 +4028,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4071,7 +4046,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -4085,14 +4060,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4111,16 +4086,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4170,7 +4145,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4188,7 +4163,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -4202,10 +4177,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4231,10 +4206,10 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4276,7 +4251,7 @@
         <v>116</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
@@ -4285,7 +4260,7 @@
         <v>145</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4317,13 +4292,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4345,13 +4320,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4402,7 +4377,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4411,7 +4386,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>120</v>
@@ -4509,16 +4484,16 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>211</v>
@@ -4539,7 +4514,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4647,7 +4622,7 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
@@ -4696,7 +4671,7 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>223</v>
@@ -4852,7 +4827,7 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Y23" t="s" s="2">
         <v>241</v>
@@ -4885,7 +4860,7 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
@@ -5234,7 +5209,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -5751,7 +5726,7 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>275</v>
@@ -5876,60 +5851,58 @@
       <c r="M32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5947,7 +5920,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5961,10 +5934,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5987,19 +5960,19 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6048,7 +6021,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6066,7 +6039,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6080,10 +6053,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6109,16 +6082,16 @@
         <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6167,7 +6140,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6185,7 +6158,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6199,10 +6172,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6228,16 +6201,16 @@
         <v>236</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6262,14 +6235,14 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6286,7 +6259,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6295,22 +6268,22 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>247</v>
@@ -6318,10 +6291,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6344,19 +6317,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6405,7 +6378,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6414,33 +6387,33 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AK36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6463,19 +6436,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6524,7 +6495,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6533,33 +6504,33 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6582,19 +6553,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6643,7 +6614,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6658,27 +6629,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6701,19 +6672,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6762,7 +6731,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6771,33 +6740,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6823,13 +6792,13 @@
         <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6837,7 +6806,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>78</v>
@@ -6879,7 +6848,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6897,13 +6866,13 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -6911,10 +6880,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6937,16 +6906,16 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6975,10 +6944,10 @@
         <v>228</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6996,7 +6965,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7014,13 +6983,13 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7028,10 +6997,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7054,19 +7023,19 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7115,7 +7084,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7124,7 +7093,7 @@
         <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -7133,13 +7102,13 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7147,10 +7116,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7262,10 +7231,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7335,16 +7304,16 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>119</v>
@@ -7379,14 +7348,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7408,10 +7377,10 @@
         <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>115</v>
@@ -7466,7 +7435,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7484,7 +7453,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7498,10 +7467,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7524,17 +7493,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7562,10 +7531,10 @@
         <v>228</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7583,7 +7552,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7601,10 +7570,10 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7615,10 +7584,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7641,17 +7610,17 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7700,7 +7669,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7718,10 +7687,10 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7732,10 +7701,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7758,19 +7727,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7819,7 +7786,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7828,33 +7795,33 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7877,19 +7844,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7938,7 +7905,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7947,22 +7914,22 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7970,10 +7937,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7996,16 +7963,16 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8055,7 +8022,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8064,7 +8031,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -8073,13 +8040,13 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8087,10 +8054,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8202,10 +8169,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8275,16 +8242,16 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>119</v>
@@ -8319,14 +8286,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8348,10 +8315,10 @@
         <v>112</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>115</v>
@@ -8406,7 +8373,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8424,7 +8391,7 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8438,10 +8405,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8464,16 +8431,16 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8502,10 +8469,10 @@
         <v>228</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8523,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>91</v>
@@ -8541,13 +8508,13 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8555,10 +8522,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8581,13 +8548,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8638,7 +8605,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8647,7 +8614,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -8656,13 +8623,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8670,10 +8637,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8696,19 +8663,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8757,7 +8724,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8766,7 +8733,7 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>103</v>
@@ -8775,13 +8742,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8789,10 +8756,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8904,10 +8871,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8977,16 +8944,16 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>119</v>
@@ -9021,14 +8988,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9050,10 +9017,10 @@
         <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>115</v>
@@ -9108,7 +9075,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9126,7 +9093,7 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9140,10 +9107,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9169,13 +9136,13 @@
         <v>236</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9201,13 +9168,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9225,7 +9192,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9234,7 +9201,7 @@
         <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9249,7 +9216,7 @@
         <v>245</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9257,10 +9224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9283,17 +9250,15 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9342,7 +9307,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9351,22 +9316,22 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>468</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9374,10 +9339,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9489,10 +9454,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9606,10 +9571,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9632,16 +9597,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9691,7 +9656,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9700,7 +9665,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9709,7 +9674,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9723,10 +9688,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9749,23 +9714,23 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>78</v>
@@ -9810,7 +9775,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9819,7 +9784,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -9828,7 +9793,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9842,10 +9807,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9868,17 +9833,15 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9927,7 +9890,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9936,16 +9899,16 @@
         <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>109</v>
@@ -9959,10 +9922,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10074,10 +10037,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10191,10 +10154,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10220,13 +10183,13 @@
         <v>105</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10276,7 +10239,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10285,7 +10248,7 @@
         <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>103</v>
@@ -10294,7 +10257,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10308,10 +10271,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10337,13 +10300,13 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10372,10 +10335,10 @@
         <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10393,7 +10356,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10411,7 +10374,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10425,10 +10388,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10454,13 +10417,13 @@
         <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10510,7 +10473,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10519,7 +10482,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -10528,7 +10491,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10542,10 +10505,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10571,13 +10534,13 @@
         <v>105</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10627,7 +10590,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10645,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10659,10 +10622,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10685,13 +10648,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10742,7 +10705,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10751,19 +10714,19 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10774,10 +10737,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10889,10 +10852,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10962,16 +10925,16 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>119</v>
@@ -11006,14 +10969,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11035,10 +10998,10 @@
         <v>112</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>115</v>
@@ -11093,7 +11056,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11111,7 +11074,7 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -11125,14 +11088,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11154,16 +11117,16 @@
         <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11212,7 +11175,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11230,10 +11193,10 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11244,10 +11207,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11273,16 +11236,16 @@
         <v>236</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11307,13 +11270,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11331,7 +11294,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11340,7 +11303,7 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
@@ -11363,10 +11326,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11389,19 +11352,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11450,7 +11411,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11459,33 +11420,33 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11508,16 +11469,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11567,7 +11528,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11576,19 +11537,19 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11599,10 +11560,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11625,16 +11586,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11684,7 +11645,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11693,7 +11654,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11702,10 +11663,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11716,10 +11677,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11742,19 +11703,19 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11782,10 +11743,10 @@
         <v>228</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11803,7 +11764,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11821,7 +11782,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>109</v>
@@ -11835,10 +11796,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11864,16 +11825,16 @@
         <v>236</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11898,13 +11859,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11922,7 +11883,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11931,7 +11892,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -11940,7 +11901,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>109</v>
@@ -11954,10 +11915,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11980,16 +11941,16 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12039,7 +12000,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12048,19 +12009,19 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12071,10 +12032,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12100,16 +12061,16 @@
         <v>236</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -12134,13 +12095,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -12158,7 +12119,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12167,7 +12128,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12176,7 +12137,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>109</v>
@@ -12190,10 +12151,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12219,13 +12180,13 @@
         <v>81</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12275,7 +12236,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12284,19 +12245,19 @@
         <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>589</v>
+        <v>546</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
